--- a/TORX DUV dates/TORX_duv_dates_df.xlsx
+++ b/TORX DUV dates/TORX_duv_dates_df.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Karina\Portfolio\TORX\TORX DUV dates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2186A91E-98A2-4024-8A76-3C46D2957D8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="25">
   <si>
     <t>Race</t>
   </si>
@@ -94,11 +100,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,13 +168,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -206,7 +220,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -240,6 +254,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -274,9 +289,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -449,11 +465,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -467,7 +486,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -481,7 +500,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -495,7 +514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -509,7 +528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -523,7 +542,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -537,7 +556,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -551,7 +570,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -565,269 +584,283 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>2025</v>
+      </c>
+      <c r="C9" s="2">
+        <v>45914.416666666664</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2">
-        <v>45179.41666666666</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C10" s="2">
+        <v>45179.416666666657</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="2">
-        <v>44451.41666666666</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" s="2">
+        <v>44451.416666666657</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="2">
-        <v>42988.41666666666</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" s="2">
+        <v>42988.416666666657</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="2">
-        <v>45543.41666666666</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" s="2">
+        <v>45543.416666666657</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="2">
-        <v>41525.41666666666</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="C14" s="2">
+        <v>41525.416666666657</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="2">
-        <v>44815.41666666666</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15" s="2">
+        <v>44815.416666666657</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2">
-        <v>41889.41666666666</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16" s="2">
+        <v>41889.416666666657</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="2">
-        <v>43716.41666666666</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" s="2">
+        <v>43716.416666666657</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="2">
-        <v>43352.41666666666</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C18" s="2">
+        <v>43352.416666666657</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="2">
-        <v>42624.41666666666</v>
-      </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C19" s="2">
+        <v>42624.416666666657</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="2">
-        <v>41161.41666666666</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C20" s="2">
+        <v>41161.416666666657</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="2">
-        <v>40797.41666666666</v>
-      </c>
-      <c r="D20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C21" s="2">
+        <v>40797.416666666657</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="2">
-        <v>42260.41666666666</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="C22" s="2">
+        <v>42260.416666666657</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="2">
-        <v>40433.41666666666</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" t="s">
-        <v>8</v>
-      </c>
       <c r="C23" s="2">
-        <v>45177.83333333334</v>
+        <v>40433.416666666657</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2">
-        <v>45541.83333333334</v>
+        <v>45177.833333333343</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2">
-        <v>44813.83333333334</v>
+        <v>45541.833333333343</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="2">
-        <v>43714.83333333334</v>
+        <v>44813.833333333343</v>
       </c>
       <c r="D26" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>6</v>
       </c>
       <c r="B27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2">
+        <v>43714.833333333343</v>
+      </c>
+      <c r="D27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="2">
-        <v>44449.83333333334</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="C28" s="2">
+        <v>44449.833333333343</v>
+      </c>
+      <c r="D28" t="s">
         <v>24</v>
       </c>
     </row>
